--- a/ejemplos/1_Contabilidad_y_Finanzas/08_Directorio_Clientes_y_Proveedores_EJEMPLO.xlsx
+++ b/ejemplos/1_Contabilidad_y_Finanzas/08_Directorio_Clientes_y_Proveedores_EJEMPLO.xlsx
@@ -53,7 +53,7 @@
     <font>
       <name val="Abadi"/>
       <b val="1"/>
-      <color rgb="001B6B73"/>
+      <color rgb="000E7C8B"/>
     </font>
     <font>
       <name val="Abadi"/>
@@ -63,7 +63,7 @@
     <font>
       <name val="Abadi"/>
       <b val="1"/>
-      <color rgb="001B6B73"/>
+      <color rgb="000E7C8B"/>
       <sz val="9"/>
     </font>
     <font>
@@ -105,7 +105,7 @@
     <font>
       <name val="Abadi"/>
       <b val="1"/>
-      <color rgb="001B6B73"/>
+      <color rgb="000E7C8B"/>
       <sz val="12"/>
     </font>
     <font>
@@ -128,7 +128,7 @@
     <font>
       <name val="Abadi"/>
       <b val="1"/>
-      <color rgb="001B6B73"/>
+      <color rgb="000E7C8B"/>
       <sz val="11"/>
     </font>
     <font>
@@ -156,7 +156,7 @@
     <font>
       <name val="Abadi"/>
       <b val="1"/>
-      <color rgb="001B6B73"/>
+      <color rgb="000E7C8B"/>
       <sz val="10"/>
     </font>
     <font>
@@ -833,7 +833,7 @@
             <idx val="0"/>
             <spPr>
               <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="1B6B73"/>
+                <a:srgbClr val="0E7C8B"/>
               </a:solidFill>
               <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
@@ -6672,7 +6672,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="001B6B73"/>
+    <tabColor rgb="000E7C8B"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>

--- a/ejemplos/1_Contabilidad_y_Finanzas/08_Directorio_Clientes_y_Proveedores_EJEMPLO.xlsx
+++ b/ejemplos/1_Contabilidad_y_Finanzas/08_Directorio_Clientes_y_Proveedores_EJEMPLO.xlsx
@@ -1233,7 +1233,7 @@
       <c r="A2" s="1" t="n"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>GRUPO CANVILLE</t>
+          <t>FORMATOS ADMINISTRATIVOS</t>
         </is>
       </c>
       <c r="C2" s="1" t="n"/>
@@ -1656,7 +1656,7 @@
       <c r="A37" s="1" t="n"/>
       <c r="B37" s="21" t="inlineStr">
         <is>
-          <t>GRUPO CANVILLE  ·  Formatos administrativos  ·  Para uso interno de tu empresa</t>
+          <t>Formatos administrativos  ·  Para uso interno de tu empresa</t>
         </is>
       </c>
       <c r="G37" s="1" t="n"/>
